--- a/reports/jobs_2026-10-26.xlsx
+++ b/reports/jobs_2026-10-26.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$105</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I111"/>
+  <dimension ref="A1:I105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -520,17 +520,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Arm India</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Payroll Industrial Trainee</t>
+          <t>Software Engineer - Jira Workflow &amp; Automation Engineering</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -550,12 +550,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8305308?gh_jid=8305308</t>
+          <t>https://careers.arm.com/job/bengaluru/software-engineer-jira-workflow-and-automation-engineering/33099/102199045568</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://careers.arm.com/</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -1103,17 +1103,17 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Theorem Proving Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/austin/theorem-proving-engineer/33099/97584421536</t>
+          <t>https://www.atlassian.com/company/careers/details/27443</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1146,17 +1146,17 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Compiler Engineer (Machine Learning)</t>
+          <t>Application Development Engineer</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1164,7 +1164,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -1172,12 +1176,12 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/lund/compiler-engineer-machine-learning/33099/94847322016</t>
+          <t>https://www.atlassian.com/company/careers/details/26833</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1194,12 +1198,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1207,7 +1211,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -1215,7 +1223,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27443</t>
+          <t>https://www.atlassian.com/company/careers/details/25539</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1237,12 +1245,12 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Application Development Engineer</t>
+          <t>Principle Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1262,7 +1270,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26833</t>
+          <t>https://www.atlassian.com/company/careers/details/27455</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1284,12 +1292,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Principle Machine Learning Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1309,7 +1317,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27455</t>
+          <t>https://www.atlassian.com/company/careers/details/25561</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1331,12 +1339,12 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Principle Machine Learning Systems Engineer</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1356,7 +1364,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25539</t>
+          <t>https://www.atlassian.com/company/careers/details/27796</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1378,12 +1386,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1391,11 +1399,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -1403,7 +1407,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25561</t>
+          <t>https://www.atlassian.com/company/careers/details/26758</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1425,12 +1429,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Principle Machine Learning Systems Engineer</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1450,7 +1454,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27796</t>
+          <t>https://www.atlassian.com/company/careers/details/25538</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1472,12 +1476,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1485,7 +1489,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -1493,7 +1501,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26758</t>
+          <t>https://www.atlassian.com/company/careers/details/27794</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1515,12 +1523,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1540,7 +1548,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25538</t>
+          <t>https://www.atlassian.com/company/careers/details/25566</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1562,12 +1570,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Software Engineer – Full Stack (Loom Billing &amp; Integrations)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1587,7 +1595,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27794</t>
+          <t>https://www.atlassian.com/company/careers/details/27431</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -1609,12 +1617,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Machine Learning System Engineer</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1634,7 +1642,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25566</t>
+          <t>https://www.atlassian.com/company/careers/details/27388</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1656,12 +1664,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack (Loom Billing &amp; Integrations)</t>
+          <t>EMEA Field CTO, DX — Engineering Executive Advisor</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1681,7 +1689,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27431</t>
+          <t>https://www.atlassian.com/company/careers/details/24899</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1703,12 +1711,12 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning System Engineer</t>
+          <t>Software Engineer, 2027 Graduate Canada</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1716,11 +1724,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E28" s="4" t="inlineStr"/>
       <c r="F28" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -1728,7 +1732,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27388</t>
+          <t>https://www.atlassian.com/company/careers/details/26070</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -1750,12 +1754,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>EMEA Field CTO, DX — Engineering Executive Advisor</t>
+          <t>Machine Learning Engineer, 2027 Graduate U.S.</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1763,11 +1767,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E29" s="4" t="inlineStr"/>
       <c r="F29" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/24899</t>
+          <t>https://www.atlassian.com/company/careers/details/25999</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, 2027 Graduate Canada</t>
+          <t>Data Engineer, 2027 Graduate U.S</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26070</t>
+          <t>https://www.atlassian.com/company/careers/details/25998</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, 2027 Graduate U.S.</t>
+          <t>Software Engineer, 2027 Graduate U.S.</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25999</t>
+          <t>https://www.atlassian.com/company/careers/details/25813</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Data Engineer, 2027 Graduate U.S</t>
+          <t>Software Engineer Intern, 2027 Canada</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25998</t>
+          <t>https://www.atlassian.com/company/careers/details/26275</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -1926,12 +1926,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, 2027 Graduate U.S.</t>
+          <t>Data Engineer Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1939,7 +1939,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -1947,7 +1951,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25813</t>
+          <t>https://www.atlassian.com/company/careers/details/26272</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -1969,7 +1973,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, 2027 Canada</t>
+          <t>Research Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1990,7 +1994,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26275</t>
+          <t>https://www.atlassian.com/company/careers/details/26270</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2012,12 +2016,12 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Data Engineer Intern, 2027 Summer U.S.</t>
+          <t>Machine Learning Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2025,11 +2029,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E35" s="4" t="inlineStr"/>
       <c r="F35" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26272</t>
+          <t>https://www.atlassian.com/company/careers/details/26268</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Research Intern, 2027 Summer U.S.</t>
+          <t>Security Engineer Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26270</t>
+          <t>https://www.atlassian.com/company/careers/details/26267</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Intern, 2027 Summer U.S.</t>
+          <t>Software Engineer Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26268</t>
+          <t>https://www.atlassian.com/company/careers/details/26266</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Security Engineer Intern, 2027 Summer U.S.</t>
+          <t>Product Design Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2158,7 +2158,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -2166,7 +2170,7 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26267</t>
+          <t>https://www.atlassian.com/company/careers/details/26273</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -2188,7 +2192,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, 2027 Summer U.S.</t>
+          <t>Product Management Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2201,7 +2205,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -2209,7 +2217,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26266</t>
+          <t>https://www.atlassian.com/company/careers/details/26274</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -2231,7 +2239,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Product Design Intern, 2027 Summer U.S.</t>
+          <t>AI Demand Intelligence Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2256,7 +2264,7 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26273</t>
+          <t>https://www.atlassian.com/company/careers/details/26843</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -2278,12 +2286,12 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Product Management Intern, 2027 Summer U.S.</t>
+          <t>Enterprise Security Engineer</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2303,7 +2311,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26274</t>
+          <t>https://www.atlassian.com/company/careers/details/27275</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -2325,12 +2333,12 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>AI Demand Intelligence Intern, 2027 Summer U.S.</t>
+          <t>Enterprise Security Engineer</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2350,7 +2358,7 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26843</t>
+          <t>https://www.atlassian.com/company/careers/details/26986</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -2372,12 +2380,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Enterprise Security Engineer</t>
+          <t>Security Testing Engineer - Penetration Tester</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2387,7 +2395,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote or Remote</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2397,7 +2405,7 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27275</t>
+          <t>https://www.atlassian.com/company/careers/details/26643</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -2414,12 +2422,12 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Chargebee</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Enterprise Security Engineer</t>
+          <t>CEO AI billing software built for founders who ship fast</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2432,11 +2440,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E44" s="4" t="inlineStr"/>
       <c r="F44" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -2444,12 +2448,12 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26986</t>
+          <t>https://www.chargebee.com/solutions/role/ceo/</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://www.chargebee.com/careers/</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -2461,17 +2465,17 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Chargebee</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Security Testing Engineer - Penetration Tester</t>
+          <t>Product Launch and price new features without waiting on engineering</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2479,11 +2483,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>Remote or Remote</t>
-        </is>
-      </c>
+      <c r="E45" s="4" t="inlineStr"/>
       <c r="F45" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -2491,12 +2491,12 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26643</t>
+          <t>https://www.chargebee.com/solutions/role/product/</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://www.chargebee.com/careers/</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>CEO AI billing software built for founders who ship fast</t>
+          <t>Growth Test offers, run promotions and lift conversion</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/solutions/role/ceo/</t>
+          <t>https://www.chargebee.com/solutions/role/growth/</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -2551,12 +2551,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Chargebee</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Product Launch and price new features without waiting on engineering</t>
+          <t>Implementation Engineer 2</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2569,7 +2569,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -2577,12 +2581,12 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/solutions/role/product/</t>
+          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -2594,17 +2598,17 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Chargebee</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Growth Test offers, run promotions and lift conversion</t>
+          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2612,7 +2616,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr"/>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>India Full-time</t>
+        </is>
+      </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -2620,12 +2628,12 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/solutions/role/growth/</t>
+          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -2642,7 +2650,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Implementation Engineer 2</t>
+          <t>Integration &amp; Customisation Engineer-3</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -2667,7 +2675,7 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
+          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer3</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -2689,12 +2697,12 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
+          <t>Integration &amp; Customization Engineer -1</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2714,7 +2722,7 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -2736,12 +2744,12 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer-3</t>
+          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -2749,11 +2757,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E51" s="4" t="inlineStr"/>
       <c r="F51" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -2761,7 +2765,7 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer3</t>
+          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -2783,7 +2787,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customization Engineer -1</t>
+          <t>Implementation Engineer</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -2798,7 +2802,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -2808,7 +2812,7 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
+          <t>https://exotel.com/about-us/careers/#op-710627-implementation-engineer</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -2830,12 +2834,12 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
+          <t>Software Engineer - 2 (Billing)</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2843,7 +2847,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr"/>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -2851,7 +2859,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-700106-software-engineer-2-billing</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -2873,7 +2881,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Implementation Engineer</t>
+          <t>Software Engineer - 3 (Voice)</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -2898,7 +2906,7 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-710627-implementation-engineer</t>
+          <t>https://exotel.com/about-us/careers/#op-704555-software-engineer-3-voice</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -2920,7 +2928,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Billing)</t>
+          <t>Forward Deployed Engineer - 2</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2945,7 +2953,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-700106-software-engineer-2-billing</t>
+          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -2967,7 +2975,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 3 (Voice)</t>
+          <t>Forward Deployed Engineer - 3</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -2992,7 +3000,7 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704555-software-engineer-3-voice</t>
+          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -3014,7 +3022,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 2</t>
+          <t>Product Head, Voice AI</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -3039,7 +3047,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
+          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -3061,12 +3069,12 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 3</t>
+          <t>Software Developer - 3 (Voice4Ai-Backend)</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3086,7 +3094,7 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
+          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-voice4aibackend</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -3108,7 +3116,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Product Head, Voice AI</t>
+          <t>Software Engineer - 2 (Voicebot)</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -3133,7 +3141,7 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
+          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -3155,7 +3163,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Software Developer - 3 (Voice4Ai-Backend)</t>
+          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -3180,7 +3188,7 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-voice4aibackend</t>
+          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -3197,12 +3205,12 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>GitLab India</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Voicebot)</t>
+          <t>Software composition analysis</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -3215,11 +3223,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E61" s="4" t="inlineStr"/>
       <c r="F61" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -3227,12 +3231,12 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
+          <t>https://about.gitlab.com/solutions/supply-chain/</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://about.gitlab.com/jobs/all-jobs/</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -3244,17 +3248,17 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -3262,11 +3266,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E62" s="4" t="inlineStr"/>
       <c r="F62" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -3274,12 +3274,12 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
@@ -3291,17 +3291,17 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Developer- WD</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Full-Stack-Developer--WD_SR-45696-1</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
@@ -3334,17 +3334,17 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Gen AI Engineer-AWS</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -3352,7 +3352,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr"/>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru-VTP, India</t>
+        </is>
+      </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -3360,12 +3364,12 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Gen-AI-Engineer-AWS_SR-47131</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
@@ -3377,17 +3381,17 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>CPGR Growth Leader, AI Engineering, Strategic Accounts</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -3395,7 +3399,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr"/>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India</t>
+        </is>
+      </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -3403,12 +3411,12 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-York/CPGR-Growth-Leader--AI-Engineering--Strategic-Accounts_SR-46966</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -3420,17 +3428,17 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -3438,7 +3446,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr"/>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>New Delhi, in</t>
+        </is>
+      </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -3446,12 +3458,12 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Data-Engineer---AWS_SR-37522</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -3463,17 +3475,17 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>GenAI-Engineer</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -3481,7 +3493,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr"/>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -3489,12 +3505,12 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/GenAI-Engineer_SR-46807</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
@@ -3506,17 +3522,17 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>GitLab India</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Software composition analysis</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -3532,12 +3548,12 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/solutions/supply-chain/</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/jobs/all-jobs/</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
@@ -3549,17 +3565,17 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -3575,12 +3591,12 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -3592,12 +3608,12 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>Cluster Head- Last mile - Chennai</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -3610,7 +3626,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr"/>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu</t>
+        </is>
+      </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -3618,12 +3638,12 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
@@ -3635,17 +3655,17 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -3653,11 +3673,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru-VTP, India</t>
-        </is>
-      </c>
+      <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -3665,12 +3681,12 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
@@ -3682,12 +3698,12 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Engineer 3 - Business Systems</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -3702,7 +3718,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -3712,12 +3728,12 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -3729,17 +3745,17 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -3747,11 +3763,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>New Delhi, in</t>
-        </is>
-      </c>
+      <c r="E73" s="4" t="inlineStr"/>
       <c r="F73" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -3759,12 +3771,12 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
@@ -3776,17 +3788,17 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>Open Financial</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>We’re hiring Build with us Roles across engineering, product and GTM.</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -3794,11 +3806,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
+      <c r="E74" s="4" t="inlineStr"/>
       <c r="F74" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -3806,12 +3814,12 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://open.money/company/careers</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://open.money/careers</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
@@ -3823,12 +3831,12 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t>Learn more about PTC internships</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -3849,12 +3857,12 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://www.ptc.com/en/careers/internships</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -3866,17 +3874,17 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Intern - Talent Acquisition</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -3884,7 +3892,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr"/>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, Haryana</t>
+        </is>
+      </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -3892,12 +3904,12 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://jobs.lever.co/paytm/426a6834-1397-4e65-94af-69874c790805</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -3909,17 +3921,17 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Cluster Head- Last mile - Chennai</t>
+          <t>Intern-Talent Acquisition</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -3929,7 +3941,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -3939,12 +3951,12 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
+          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
@@ -3956,17 +3968,17 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>Internship - Talent Acquisition</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -3974,7 +3986,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr"/>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -3982,12 +3998,12 @@
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
@@ -3999,17 +4015,17 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Engineer 3 - Business Systems</t>
+          <t>Talent Acquisition Intern</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -4019,7 +4035,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -4029,12 +4045,12 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
+          <t>https://jobs.lever.co/paytm/6d7551f7-34c3-46a2-a4e4-18b29f15338c</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
@@ -4046,17 +4062,17 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t>Talent Acquisition Intern - Bangalore</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -4064,7 +4080,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr"/>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -4072,12 +4092,12 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
@@ -4089,17 +4109,17 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Open Financial</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>We’re hiring Build with us Roles across engineering, product and GTM.</t>
+          <t>Talent Acquisition Intern - IT Recruitment</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -4107,7 +4127,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr"/>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -4115,12 +4139,12 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>https://open.money/company/careers</t>
+          <t>https://jobs.lever.co/paytm/95eadc2b-27bf-40fe-b6e6-93aaeadd08f7</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>https://open.money/careers</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
@@ -4132,17 +4156,17 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Learn more about PTC internships</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -4158,12 +4182,12 @@
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers/internships</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
@@ -4175,17 +4199,17 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Intern - Talent Acquisition</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -4195,7 +4219,7 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, Haryana</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -4205,12 +4229,12 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/426a6834-1397-4e65-94af-69874c790805</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
@@ -4222,17 +4246,17 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Intern-Talent Acquisition</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -4242,7 +4266,7 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -4252,12 +4276,12 @@
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
@@ -4269,17 +4293,17 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Internship - Talent Acquisition</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -4289,7 +4313,7 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -4299,12 +4323,12 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
@@ -4316,12 +4340,12 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -4334,11 +4358,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>Noida, Uttar Pradesh</t>
-        </is>
-      </c>
+      <c r="E86" s="4" t="inlineStr"/>
       <c r="F86" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -4346,12 +4366,12 @@
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/6d7551f7-34c3-46a2-a4e4-18b29f15338c</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr">
@@ -4363,12 +4383,12 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Bangalore</t>
+          <t>ENG Project/ Program - Intern</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -4383,7 +4403,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -4393,12 +4413,12 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
@@ -4410,17 +4430,17 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - IT Recruitment</t>
+          <t>Industrial Trainee</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -4430,7 +4450,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -4440,12 +4460,12 @@
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/95eadc2b-27bf-40fe-b6e6-93aaeadd08f7</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8266405?gh_jid=8266405</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr">
@@ -4457,12 +4477,12 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>Payroll Industrial Trainee</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -4475,7 +4495,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr"/>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -4483,12 +4507,12 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8305308?gh_jid=8305308</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
@@ -4500,17 +4524,17 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t xml:space="preserve">Security Engineer - Identity and Access </t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -4520,7 +4544,7 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
@@ -4530,12 +4554,12 @@
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
@@ -4547,12 +4571,12 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>Software Engineer - Cloud: Azure</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -4562,12 +4586,12 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>0-2 years</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t xml:space="preserve">Bangalore </t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -4577,12 +4601,12 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8258200?gh_jid=8258200</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
@@ -4594,17 +4618,17 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>Software Engineer - IAM</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -4614,7 +4638,7 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
@@ -4624,12 +4648,12 @@
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
@@ -4641,12 +4665,12 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -4667,12 +4691,12 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzgsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
@@ -4684,17 +4708,17 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>ENG Project/ Program - Intern</t>
+          <t>AI Screenplay Writer</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -4702,11 +4726,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E94" s="4" t="inlineStr"/>
       <c r="F94" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -4714,12 +4734,12 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzMsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
@@ -4731,12 +4751,12 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Industrial Trainee</t>
+          <t>AI Video Editor</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -4749,11 +4769,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E95" s="4" t="inlineStr"/>
       <c r="F95" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -4761,12 +4777,12 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8266405?gh_jid=8266405</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTIsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
@@ -4778,12 +4794,12 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security Engineer - Identity and Access </t>
+          <t>AI Sound Designer</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -4796,11 +4812,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, India</t>
-        </is>
-      </c>
+      <c r="E96" s="4" t="inlineStr"/>
       <c r="F96" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -4808,12 +4820,12 @@
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr">
@@ -4825,12 +4837,12 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud: Azure</t>
+          <t>AI Animator</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -4840,14 +4852,10 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>0-2 years</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bangalore </t>
-        </is>
-      </c>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr"/>
       <c r="F97" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -4855,12 +4863,12 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8258200?gh_jid=8258200</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
@@ -4872,17 +4880,17 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - IAM</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -4892,7 +4900,7 @@
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
@@ -4902,12 +4910,12 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
@@ -4919,17 +4927,17 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -4937,7 +4945,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr"/>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -4945,12 +4957,12 @@
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzgsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
@@ -4962,17 +4974,17 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>SirionLabs</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>AI Screenplay Writer</t>
+          <t>Intern- Employee Engagement</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -4988,12 +5000,12 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzMsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.sirion.ai/jobs/intern-employee-engagement/</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://www.sirionlabs.com/careers/</t>
         </is>
       </c>
       <c r="I100" s="4" t="inlineStr">
@@ -5005,17 +5017,17 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Sprinklr</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>AI Video Editor</t>
+          <t>Internship and Early Careers</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -5031,12 +5043,12 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTIsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://www.sprinklr.com/careers/</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
@@ -5048,17 +5060,17 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Stripe India</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>AI Sound Designer</t>
+          <t>Software Engineer, Intern</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -5066,7 +5078,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr"/>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -5074,12 +5090,12 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://boards.greenhouse.io/stripe</t>
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr">
@@ -5091,12 +5107,12 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Unacademy</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>AI Animator</t>
+          <t>Test Jerin</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -5109,7 +5125,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr"/>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -5117,12 +5137,12 @@
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
@@ -5134,17 +5154,17 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>Unacademy</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -5154,7 +5174,7 @@
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, in</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
@@ -5164,12 +5184,12 @@
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr">
@@ -5181,17 +5201,17 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>Zscaler India</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+          <t>Escalation Engineer</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -5201,7 +5221,7 @@
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, in</t>
+          <t>Bangalore, IND</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
@@ -5211,12 +5231,12 @@
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+          <t>https://job-boards.greenhouse.io/zscaler/jobs/5263563007</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://boards.greenhouse.io/zscaler</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
@@ -5225,282 +5245,8 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="4" t="inlineStr">
-        <is>
-          <t>SirionLabs</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>Intern- Employee Engagement</t>
-        </is>
-      </c>
-      <c r="C106" s="4" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D106" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E106" s="4" t="inlineStr"/>
-      <c r="F106" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="G106" s="5" t="inlineStr">
-        <is>
-          <t>https://www.sirion.ai/jobs/intern-employee-engagement/</t>
-        </is>
-      </c>
-      <c r="H106" s="4" t="inlineStr">
-        <is>
-          <t>https://www.sirionlabs.com/careers/</t>
-        </is>
-      </c>
-      <c r="I106" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t>Sprinklr</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>Internship and Early Careers</t>
-        </is>
-      </c>
-      <c r="C107" s="4" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr"/>
-      <c r="F107" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="G107" s="5" t="inlineStr">
-        <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
-        </is>
-      </c>
-      <c r="H107" s="4" t="inlineStr">
-        <is>
-          <t>https://www.sprinklr.com/careers/</t>
-        </is>
-      </c>
-      <c r="I107" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="4" t="inlineStr">
-        <is>
-          <t>Stripe India</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>Software Engineer, Intern</t>
-        </is>
-      </c>
-      <c r="C108" s="4" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D108" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E108" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F108" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="G108" s="5" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
-        </is>
-      </c>
-      <c r="H108" s="4" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/stripe</t>
-        </is>
-      </c>
-      <c r="I108" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="4" t="inlineStr">
-        <is>
-          <t>Unacademy</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>Test Jerin</t>
-        </is>
-      </c>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D109" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="G109" s="5" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
-        </is>
-      </c>
-      <c r="H109" s="4" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
-        </is>
-      </c>
-      <c r="I109" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="4" t="inlineStr">
-        <is>
-          <t>Unacademy</t>
-        </is>
-      </c>
-      <c r="B110" s="4" t="inlineStr">
-        <is>
-          <t>Software Engineer, Backend</t>
-        </is>
-      </c>
-      <c r="C110" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="D110" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="G110" s="5" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
-        </is>
-      </c>
-      <c r="H110" s="4" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
-        </is>
-      </c>
-      <c r="I110" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t>Zscaler India</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
-        <is>
-          <t>Escalation Engineer</t>
-        </is>
-      </c>
-      <c r="C111" s="4" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D111" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, IND</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="G111" s="5" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/zscaler/jobs/5263563007</t>
-        </is>
-      </c>
-      <c r="H111" s="4" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/zscaler</t>
-        </is>
-      </c>
-      <c r="I111" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I111"/>
+  <autoFilter ref="A1:I105"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -5606,12 +5352,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId110"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5623,7 +5363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5691,15 +5431,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Log9 Materials</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.log9materials.com/careers</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.log9materials.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Signzy</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>https://www.signzy.com/careers/</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5708,26 +5468,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Log9 Materials</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://www.log9materials.com/careers</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.log9materials.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -5891,35 +5631,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FirstCry</t>
+          <t>Zomato</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.firstcry.com/careers</t>
+          <t>https://www.zomato.com/careers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.firstcry.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Zomato</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>https://www.zomato.com/careers</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -5928,18 +5648,18 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Swiggy</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>https://careers.swiggy.com/</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5948,18 +5668,18 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Coforge</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>https://www.coforge.com/careers</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -5968,18 +5688,18 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -5988,18 +5708,18 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
